--- a/static/templates/Mau_import_hoc_sinh.xlsx
+++ b/static/templates/Mau_import_hoc_sinh.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách học sinh" sheetId="1" r:id="R4ca192d3e96b4be8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danh sách học sinh" sheetId="1" r:id="R463b476b51d648cf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -362,7 +362,7 @@
         <x:v>Ngày nhập học</x:v>
       </x:c>
     </x:row>
-    <x:row r="5">
+    <x:row r="5" ht="22" customHeight="1">
       <x:c r="A5" s="12" t="str">
         <x:v>Nguyễn Văn A</x:v>
       </x:c>
@@ -376,7 +376,7 @@
         <x:v>15/07/2026</x:v>
       </x:c>
     </x:row>
-    <x:row r="6">
+    <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="12" t="str">
         <x:v>Trần Thị B</x:v>
       </x:c>
@@ -388,117 +388,173 @@
       </x:c>
       <x:c r="D6" s="15" t="str"/>
     </x:row>
-    <x:row r="7">
-      <x:c r="B7" s="14"/>
-      <x:c r="D7" s="16"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="B8" s="14"/>
-      <x:c r="D8" s="16"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="B9" s="14"/>
-      <x:c r="D9" s="16"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="B10" s="14"/>
-      <x:c r="D10" s="16"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="B11" s="14"/>
-      <x:c r="D11" s="16"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="B12" s="14"/>
-      <x:c r="D12" s="16"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="B13" s="14"/>
-      <x:c r="D13" s="16"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="B14" s="14"/>
-      <x:c r="D14" s="16"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="B15" s="14"/>
-      <x:c r="D15" s="16"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="B16" s="14"/>
-      <x:c r="D16" s="16"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="B17" s="14"/>
-      <x:c r="D17" s="16"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="B18" s="14"/>
-      <x:c r="D18" s="16"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="B19" s="14"/>
-      <x:c r="D19" s="16"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="B20" s="14"/>
-      <x:c r="D20" s="16"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="B21" s="14"/>
-      <x:c r="D21" s="16"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="B22" s="14"/>
-      <x:c r="D22" s="16"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="B23" s="14"/>
-      <x:c r="D23" s="16"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="B24" s="14"/>
-      <x:c r="D24" s="16"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="B25" s="14"/>
-      <x:c r="D25" s="16"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="B26" s="14"/>
-      <x:c r="D26" s="16"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="B27" s="14"/>
-      <x:c r="D27" s="16"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="B28" s="14"/>
-      <x:c r="D28" s="16"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="B29" s="14"/>
-      <x:c r="D29" s="16"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="B30" s="14"/>
-      <x:c r="D30" s="16"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="B31" s="14"/>
-      <x:c r="D31" s="16"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="B32" s="14"/>
-      <x:c r="D32" s="16"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="B33" s="14"/>
-      <x:c r="D33" s="16"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="B34" s="14"/>
-      <x:c r="D34" s="16"/>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="12"/>
+      <x:c r="B7" s="13"/>
+      <x:c r="C7" s="12"/>
+      <x:c r="D7" s="15"/>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="12"/>
+      <x:c r="B8" s="13"/>
+      <x:c r="C8" s="12"/>
+      <x:c r="D8" s="15"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="12"/>
+      <x:c r="B9" s="13"/>
+      <x:c r="C9" s="12"/>
+      <x:c r="D9" s="15"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="12"/>
+      <x:c r="B10" s="13"/>
+      <x:c r="C10" s="12"/>
+      <x:c r="D10" s="15"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="12"/>
+      <x:c r="B11" s="13"/>
+      <x:c r="C11" s="12"/>
+      <x:c r="D11" s="15"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="12"/>
+      <x:c r="B12" s="13"/>
+      <x:c r="C12" s="12"/>
+      <x:c r="D12" s="15"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="12"/>
+      <x:c r="B13" s="13"/>
+      <x:c r="C13" s="12"/>
+      <x:c r="D13" s="15"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="12"/>
+      <x:c r="B14" s="13"/>
+      <x:c r="C14" s="12"/>
+      <x:c r="D14" s="15"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="12"/>
+      <x:c r="B15" s="13"/>
+      <x:c r="C15" s="12"/>
+      <x:c r="D15" s="15"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="12"/>
+      <x:c r="B16" s="13"/>
+      <x:c r="C16" s="12"/>
+      <x:c r="D16" s="15"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="12"/>
+      <x:c r="B17" s="13"/>
+      <x:c r="C17" s="12"/>
+      <x:c r="D17" s="15"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="12"/>
+      <x:c r="B18" s="13"/>
+      <x:c r="C18" s="12"/>
+      <x:c r="D18" s="15"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="12"/>
+      <x:c r="B19" s="13"/>
+      <x:c r="C19" s="12"/>
+      <x:c r="D19" s="15"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="12"/>
+      <x:c r="B20" s="13"/>
+      <x:c r="C20" s="12"/>
+      <x:c r="D20" s="15"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="12"/>
+      <x:c r="B21" s="13"/>
+      <x:c r="C21" s="12"/>
+      <x:c r="D21" s="15"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="12"/>
+      <x:c r="B22" s="13"/>
+      <x:c r="C22" s="12"/>
+      <x:c r="D22" s="15"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="12"/>
+      <x:c r="B23" s="13"/>
+      <x:c r="C23" s="12"/>
+      <x:c r="D23" s="15"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="12"/>
+      <x:c r="B24" s="13"/>
+      <x:c r="C24" s="12"/>
+      <x:c r="D24" s="15"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="12"/>
+      <x:c r="B25" s="13"/>
+      <x:c r="C25" s="12"/>
+      <x:c r="D25" s="15"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="12"/>
+      <x:c r="B26" s="13"/>
+      <x:c r="C26" s="12"/>
+      <x:c r="D26" s="15"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="12"/>
+      <x:c r="B27" s="13"/>
+      <x:c r="C27" s="12"/>
+      <x:c r="D27" s="15"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="12"/>
+      <x:c r="B28" s="13"/>
+      <x:c r="C28" s="12"/>
+      <x:c r="D28" s="15"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="12"/>
+      <x:c r="B29" s="13"/>
+      <x:c r="C29" s="12"/>
+      <x:c r="D29" s="15"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="12"/>
+      <x:c r="B30" s="13"/>
+      <x:c r="C30" s="12"/>
+      <x:c r="D30" s="15"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="12"/>
+      <x:c r="B31" s="13"/>
+      <x:c r="C31" s="12"/>
+      <x:c r="D31" s="15"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="12"/>
+      <x:c r="B32" s="13"/>
+      <x:c r="C32" s="12"/>
+      <x:c r="D32" s="15"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="12"/>
+      <x:c r="B33" s="13"/>
+      <x:c r="C33" s="12"/>
+      <x:c r="D33" s="15"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="12"/>
+      <x:c r="B34" s="13"/>
+      <x:c r="C34" s="12"/>
+      <x:c r="D34" s="15"/>
     </x:row>
     <x:row r="35">
       <x:c r="B35" s="14"/>
